--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.10_b0.10_x0.10_Q4_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.10_b0.10_x0.10_Q4_LO.xlsx
@@ -455,13 +455,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.00931098741055234</v>
+        <v>0.009447540659166418</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00931098741055234</v>
+        <v>0.009447540659166418</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004603471021179731</v>
+        <v>0.004977250483554236</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +469,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.009142733402061252</v>
+        <v>0.009288627166828142</v>
       </c>
       <c r="C3" t="n">
-        <v>0.009142733402061252</v>
+        <v>0.009288627166828142</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004838905023214949</v>
+        <v>0.005246775375791481</v>
       </c>
     </row>
     <row r="4">
@@ -483,13 +483,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.009164149222511297</v>
+        <v>0.009305185459676459</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009164149222511297</v>
+        <v>0.009305185459676459</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004706422782305968</v>
+        <v>0.005070333564219746</v>
       </c>
     </row>
     <row r="5">
@@ -497,13 +497,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.009165675076613568</v>
+        <v>0.009293688037640024</v>
       </c>
       <c r="C5" t="n">
-        <v>0.009165675076613568</v>
+        <v>0.009293688037640024</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004599152426730061</v>
+        <v>0.004907393558911176</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +511,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.00908066291139082</v>
+        <v>0.009190061937873903</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00908066291139082</v>
+        <v>0.009190061937873903</v>
       </c>
       <c r="D6" t="n">
-        <v>0.004517647378315322</v>
+        <v>0.004769819590989272</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.009013871822723996</v>
+        <v>0.00910318285699227</v>
       </c>
       <c r="C7" t="n">
-        <v>0.009013871822723996</v>
+        <v>0.00910318285699227</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00443996127434602</v>
+        <v>0.004625612771202482</v>
       </c>
     </row>
     <row r="8">
@@ -539,13 +539,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.008894897830793256</v>
+        <v>0.008961782665151796</v>
       </c>
       <c r="C8" t="n">
-        <v>0.008894897830793256</v>
+        <v>0.008961782665151796</v>
       </c>
       <c r="D8" t="n">
-        <v>0.004376677788942771</v>
+        <v>0.004489152325321899</v>
       </c>
     </row>
     <row r="9">
@@ -553,13 +553,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.008765451904587315</v>
+        <v>0.008809454651370074</v>
       </c>
       <c r="C9" t="n">
-        <v>0.008765451904587315</v>
+        <v>0.008809454651370074</v>
       </c>
       <c r="D9" t="n">
-        <v>0.004316618231512255</v>
+        <v>0.004358187800949338</v>
       </c>
     </row>
     <row r="10">
@@ -567,13 +567,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.008628472018280282</v>
+        <v>0.008650086794539337</v>
       </c>
       <c r="C10" t="n">
-        <v>0.008628472018280282</v>
+        <v>0.008650086794539337</v>
       </c>
       <c r="D10" t="n">
-        <v>0.00425265450444817</v>
+        <v>0.004229968122960135</v>
       </c>
     </row>
     <row r="11">
@@ -581,13 +581,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.008489869441436983</v>
+        <v>0.008491537711849951</v>
       </c>
       <c r="C11" t="n">
-        <v>0.008489869441436983</v>
+        <v>0.008491537711849951</v>
       </c>
       <c r="D11" t="n">
-        <v>0.004176261913591002</v>
+        <v>0.004099902955268425</v>
       </c>
     </row>
     <row r="12">
@@ -595,13 +595,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.008356852861905514</v>
+        <v>0.008339476835126996</v>
       </c>
       <c r="C12" t="n">
-        <v>0.008356852861905514</v>
+        <v>0.008339476835126996</v>
       </c>
       <c r="D12" t="n">
-        <v>0.004083040059731674</v>
+        <v>0.003965073765554875</v>
       </c>
     </row>
     <row r="13">
@@ -609,13 +609,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.008234712685582396</v>
+        <v>0.008201923324769312</v>
       </c>
       <c r="C13" t="n">
-        <v>0.008234712685582396</v>
+        <v>0.008201923324769312</v>
       </c>
       <c r="D13" t="n">
-        <v>0.003973147863312895</v>
+        <v>0.003829001649196759</v>
       </c>
     </row>
     <row r="14">
@@ -623,13 +623,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.008128252776158557</v>
+        <v>0.008083228516869666</v>
       </c>
       <c r="C14" t="n">
-        <v>0.008128252776158557</v>
+        <v>0.008083228516869666</v>
       </c>
       <c r="D14" t="n">
-        <v>0.003847363694574393</v>
+        <v>0.003688576496263887</v>
       </c>
     </row>
     <row r="15">
@@ -637,13 +637,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.008039230662109428</v>
+        <v>0.007985160837067585</v>
       </c>
       <c r="C15" t="n">
-        <v>0.008039230662109428</v>
+        <v>0.007985160837067585</v>
       </c>
       <c r="D15" t="n">
-        <v>0.003707644222488295</v>
+        <v>0.003545665799398164</v>
       </c>
     </row>
     <row r="16">
@@ -651,13 +651,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.007968553334797972</v>
+        <v>0.007908533022395269</v>
       </c>
       <c r="C16" t="n">
-        <v>0.007968553334797972</v>
+        <v>0.007908533022395269</v>
       </c>
       <c r="D16" t="n">
-        <v>0.003554211899534564</v>
+        <v>0.003399756777733629</v>
       </c>
     </row>
     <row r="17">
@@ -665,13 +665,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.007917564849882829</v>
+        <v>0.007854576689618758</v>
       </c>
       <c r="C17" t="n">
-        <v>0.007917564849882829</v>
+        <v>0.007854576689618758</v>
       </c>
       <c r="D17" t="n">
-        <v>0.003392350430372918</v>
+        <v>0.003252436615524848</v>
       </c>
     </row>
     <row r="18">
@@ -679,13 +679,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.007888768794719845</v>
+        <v>0.007825709633152005</v>
       </c>
       <c r="C18" t="n">
-        <v>0.007888768794719845</v>
+        <v>0.007825709633152005</v>
       </c>
       <c r="D18" t="n">
-        <v>0.003222831093506925</v>
+        <v>0.003110979922392869</v>
       </c>
     </row>
     <row r="19">
@@ -693,13 +693,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.007885259028145816</v>
+        <v>0.007824933808842041</v>
       </c>
       <c r="C19" t="n">
-        <v>0.007885259028145816</v>
+        <v>0.007824933808842041</v>
       </c>
       <c r="D19" t="n">
-        <v>0.003051683103270668</v>
+        <v>0.002971189471332576</v>
       </c>
     </row>
     <row r="20">
@@ -707,13 +707,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.007910099425792752</v>
+        <v>0.0078552122499777</v>
       </c>
       <c r="C20" t="n">
-        <v>0.007910099425792752</v>
+        <v>0.0078552122499777</v>
       </c>
       <c r="D20" t="n">
-        <v>0.002882785928680816</v>
+        <v>0.00284208866333746</v>
       </c>
     </row>
     <row r="21">
@@ -721,13 +721,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.007965267512678016</v>
+        <v>0.007918297816560388</v>
       </c>
       <c r="C21" t="n">
-        <v>0.007965267512678016</v>
+        <v>0.007918297816560388</v>
       </c>
       <c r="D21" t="n">
-        <v>0.00272318753792267</v>
+        <v>0.002731604568070152</v>
       </c>
     </row>
     <row r="22">
@@ -735,13 +735,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.008053760524077191</v>
+        <v>0.008017197641903593</v>
       </c>
       <c r="C22" t="n">
-        <v>0.008053760524077191</v>
+        <v>0.008017197641903593</v>
       </c>
       <c r="D22" t="n">
-        <v>0.002575155095140039</v>
+        <v>0.002628622639581238</v>
       </c>
     </row>
     <row r="23">
@@ -749,13 +749,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.008176699171294353</v>
+        <v>0.00815288269211706</v>
       </c>
       <c r="C23" t="n">
-        <v>0.008176699171294353</v>
+        <v>0.00815288269211706</v>
       </c>
       <c r="D23" t="n">
-        <v>0.002448590808827388</v>
+        <v>0.002553690006452447</v>
       </c>
     </row>
     <row r="24">
@@ -763,13 +763,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.008335312037860431</v>
+        <v>0.008305918280667377</v>
       </c>
       <c r="C24" t="n">
-        <v>0.008335312037860431</v>
+        <v>0.008305918280667377</v>
       </c>
       <c r="D24" t="n">
-        <v>0.002351196327296073</v>
+        <v>0.0025080037064518</v>
       </c>
     </row>
     <row r="25">
@@ -777,13 +777,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.008505044334397515</v>
+        <v>0.008511839727484012</v>
       </c>
       <c r="C25" t="n">
-        <v>0.008505044334397515</v>
+        <v>0.008511839727484012</v>
       </c>
       <c r="D25" t="n">
-        <v>0.002280632844973584</v>
+        <v>0.002483728490835091</v>
       </c>
     </row>
     <row r="26">
@@ -791,13 +791,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.008734512611257315</v>
+        <v>0.008760024811143692</v>
       </c>
       <c r="C26" t="n">
-        <v>0.008734512611257315</v>
+        <v>0.008760024811143692</v>
       </c>
       <c r="D26" t="n">
-        <v>0.002232212595625422</v>
+        <v>0.002480962961465634</v>
       </c>
     </row>
     <row r="27">
@@ -805,13 +805,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.009006449954790254</v>
+        <v>0.009052147591836496</v>
       </c>
       <c r="C27" t="n">
-        <v>0.009006449954790254</v>
+        <v>0.009052147591836496</v>
       </c>
       <c r="D27" t="n">
-        <v>0.002214687272468547</v>
+        <v>0.002498351619345077</v>
       </c>
     </row>
     <row r="28">
@@ -819,13 +819,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.009322231389955112</v>
+        <v>0.009389899171145957</v>
       </c>
       <c r="C28" t="n">
-        <v>0.009322231389955112</v>
+        <v>0.009389899171145957</v>
       </c>
       <c r="D28" t="n">
-        <v>0.002220605623991716</v>
+        <v>0.002531659131293402</v>
       </c>
     </row>
     <row r="29">
@@ -833,13 +833,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.009683071798847368</v>
+        <v>0.00977433841999357</v>
       </c>
       <c r="C29" t="n">
-        <v>0.009683071798847368</v>
+        <v>0.00977433841999357</v>
       </c>
       <c r="D29" t="n">
-        <v>0.002249703129342002</v>
+        <v>0.002575143641305853</v>
       </c>
     </row>
     <row r="30">
@@ -847,13 +847,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.01008964256485899</v>
+        <v>0.01020608965498091</v>
       </c>
       <c r="C30" t="n">
-        <v>0.01008964256485899</v>
+        <v>0.01020608965498091</v>
       </c>
       <c r="D30" t="n">
-        <v>0.002292957392931558</v>
+        <v>0.002626375072246411</v>
       </c>
     </row>
     <row r="31">
@@ -861,13 +861,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.01054236224984497</v>
+        <v>0.01068546876538306</v>
       </c>
       <c r="C31" t="n">
-        <v>0.01054236224984497</v>
+        <v>0.01068546876538306</v>
       </c>
       <c r="D31" t="n">
-        <v>0.002349970385962569</v>
+        <v>0.002687405489336276</v>
       </c>
     </row>
   </sheetData>
